--- a/artfynd/A 8323-2023 artfynd.xlsx
+++ b/artfynd/A 8323-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8323-2023 artfynd.xlsx
+++ b/artfynd/A 8323-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109350412</v>
+        <v>109350600</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallmo källa, 275 m NV om, Upl</t>
+          <t>Vallmo källa, 300 m NV om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629155.6924153067</v>
+        <v>629219</v>
       </c>
       <c r="R2" t="n">
-        <v>6649892.562943731</v>
+        <v>6649956</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,19 +746,9 @@
           <t>2023-05-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +763,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109350310</v>
+        <v>100358800</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,41 +816,52 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vallmo källa, 250 m NV om, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629124.9174820004</v>
+        <v>629218</v>
       </c>
       <c r="R3" t="n">
-        <v>6649853.901375642</v>
+        <v>6649641</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +885,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,43 +899,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Tallskog på blockmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn, Margaux Boeraeve</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109350600</v>
+        <v>115674376</v>
       </c>
       <c r="B4" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,40 +928,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallmo källa, 300 m NV om, Upl</t>
+          <t>Styggkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629218.7159420814</v>
+        <v>628926</v>
       </c>
       <c r="R4" t="n">
-        <v>6649956.406949371</v>
+        <v>6649849</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,22 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,100 +996,80 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>2023:12</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Erik Sjödin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Viktor Lund</t>
+          <t>Erik Sjödin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+          <t>Personlig inventering NES</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109350258</v>
+        <v>109350412</v>
       </c>
       <c r="B5" t="n">
-        <v>89776</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6040162</v>
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallmo källa, 400 m väster om, Upl</t>
+          <t>Vallmo källa, 275 m NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628946.7146127389</v>
+        <v>629156</v>
       </c>
       <c r="R5" t="n">
-        <v>6649638.19246769</v>
+        <v>6649893</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,19 +1099,9 @@
           <t>2023-05-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,27 +1116,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1213,6 +1131,251 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>109350310</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vallmo källa, 250 m NV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>629125</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6649854</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>109350258</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vallmo källa, 400 m väster om, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>628947</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6649638</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
